--- a/applications/Body_GravityPara_Iden/build/full_dynamics_validation_summary.xlsx
+++ b/applications/Body_GravityPara_Iden/build/full_dynamics_validation_summary.xlsx
@@ -16,7 +16,118 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+  <si>
+    <t>id_rmse</t>
+  </si>
+  <si>
+    <t>cad</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>phys</t>
+  </si>
+  <si>
+    <t>fd</t>
+  </si>
+  <si>
+    <t>j1</t>
+  </si>
+  <si>
+    <t>j2</t>
+  </si>
+  <si>
+    <t>j3</t>
+  </si>
+  <si>
+    <t>j4</t>
+  </si>
+  <si>
+    <t>j5</t>
+  </si>
+  <si>
+    <t>j6</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>fd_rmse</t>
+  </si>
+  <si>
+    <t>qd_cad</t>
+  </si>
+  <si>
+    <t>qd_min</t>
+  </si>
+  <si>
+    <t>qd_rec</t>
+  </si>
+  <si>
+    <t>qd_phys</t>
+  </si>
+  <si>
+    <t>qd_fd</t>
+  </si>
+  <si>
+    <t>cad</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>phys</t>
+  </si>
+  <si>
+    <t>fd</t>
+  </si>
+  <si>
+    <t>j1</t>
+  </si>
+  <si>
+    <t>j2</t>
+  </si>
+  <si>
+    <t>j3</t>
+  </si>
+  <si>
+    <t>j4</t>
+  </si>
+  <si>
+    <t>j5</t>
+  </si>
+  <si>
+    <t>j6</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>csv_file</t>
+  </si>
+  <si>
+    <t>/home/lsn/model/model_e1/applications/Body_GravityPara_Iden/test/../data/excitation/PD-M1-v0_multi_joint_20260305-195432_exctra_real.csv</t>
+  </si>
+  <si>
+    <t>num_samples</t>
+  </si>
+  <si>
+    <t>num_fd_samples</t>
+  </si>
   <si>
     <t>id_rmse</t>
   </si>
@@ -258,7 +369,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -272,11 +383,14 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
@@ -284,6 +398,9 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -309,36 +426,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="B2" s="0">
         <v>25.133675083377792</v>
@@ -367,7 +484,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="B3" s="0">
         <v>21.76313210642531</v>
@@ -396,7 +513,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="B4" s="0">
         <v>21.783348040775511</v>
@@ -425,7 +542,7 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="B5" s="0">
         <v>23.393958287947715</v>
@@ -454,31 +571,31 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="B6" s="0">
-        <v>23.294662857677331</v>
+        <v>23.349844310268359</v>
       </c>
       <c r="C6" s="0">
-        <v>15.131116111709817</v>
+        <v>15.125486826265215</v>
       </c>
       <c r="D6" s="0">
-        <v>24.368183282391254</v>
+        <v>24.395029752892562</v>
       </c>
       <c r="E6" s="0">
-        <v>8.8738722865902382</v>
+        <v>8.8720674070851313</v>
       </c>
       <c r="F6" s="0">
-        <v>3.6949942730592902</v>
+        <v>3.4283165714995985</v>
       </c>
       <c r="G6" s="0">
-        <v>0.94006287212114803</v>
+        <v>0.76713572416961928</v>
       </c>
       <c r="H6" s="0">
-        <v>12.717148613924847</v>
+        <v>12.65631343203008</v>
       </c>
       <c r="I6" s="0">
-        <v>24.368183282391254</v>
+        <v>24.395029752892562</v>
       </c>
     </row>
   </sheetData>
@@ -503,36 +620,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="B2" s="0">
         <v>17.330921290213421</v>
@@ -561,7 +678,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="B3" s="0">
         <v>27328908.772966035</v>
@@ -590,7 +707,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="B4" s="0">
         <v>27444377.805836305</v>
@@ -619,7 +736,7 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="B5" s="0">
         <v>36.899047493615598</v>
@@ -648,36 +765,36 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="B6" s="0">
-        <v>3039830.4825902381</v>
+        <v>5.893327064238548</v>
       </c>
       <c r="C6" s="0">
-        <v>969157.44328354904</v>
+        <v>3.205755268369749</v>
       </c>
       <c r="D6" s="0">
-        <v>623680.27278145473</v>
+        <v>2.047774379467783</v>
       </c>
       <c r="E6" s="0">
-        <v>10574901.676863665</v>
+        <v>11.980768156016866</v>
       </c>
       <c r="F6" s="0">
-        <v>48562645.395575166</v>
+        <v>85.175371572471064</v>
       </c>
       <c r="G6" s="0">
-        <v>3127892.3762459387</v>
+        <v>6.8901975613367892</v>
       </c>
       <c r="H6" s="0">
-        <v>11149684.607890001</v>
+        <v>19.198865666983469</v>
       </c>
       <c r="I6" s="0">
-        <v>48562645.395575166</v>
+        <v>85.175371572471064</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="B7" s="0">
         <v>98.413153420524665</v>
@@ -706,7 +823,7 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="B8" s="0">
         <v>117492551.97978444</v>
@@ -735,7 +852,7 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="B9" s="0">
         <v>117706796.78119019</v>
@@ -764,7 +881,7 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="B10" s="0">
         <v>200.9907955086567</v>
@@ -793,31 +910,31 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="B11" s="0">
-        <v>14705780.66082767</v>
+        <v>66.101355342056308</v>
       </c>
       <c r="C11" s="0">
-        <v>5252214.5733067989</v>
+        <v>41.695882512290808</v>
       </c>
       <c r="D11" s="0">
-        <v>3109457.0794662908</v>
+        <v>30.262015826549664</v>
       </c>
       <c r="E11" s="0">
-        <v>51031384.17338673</v>
+        <v>50.344564545196675</v>
       </c>
       <c r="F11" s="0">
-        <v>236110438.27936482</v>
+        <v>356.63419090270077</v>
       </c>
       <c r="G11" s="0">
-        <v>34283667.550402738</v>
+        <v>82.015430216359235</v>
       </c>
       <c r="H11" s="0">
-        <v>57415490.38612584</v>
+        <v>104.50890655752558</v>
       </c>
       <c r="I11" s="0">
-        <v>236110438.27936482</v>
+        <v>356.63419090270077</v>
       </c>
     </row>
   </sheetData>
@@ -836,18 +953,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="B2" s="0">
         <v>1001</v>

--- a/applications/Body_GravityPara_Iden/build/full_dynamics_validation_summary.xlsx
+++ b/applications/Body_GravityPara_Iden/build/full_dynamics_validation_summary.xlsx
@@ -9,6 +9,10 @@
     <sheet name="ID_RMSE" sheetId="2" r:id="rId3"/>
     <sheet name="FD_RMSE" sheetId="3" r:id="rId5"/>
     <sheet name="Meta" sheetId="4" r:id="rId6"/>
+    <sheet name="ID_PLOT_FILES" sheetId="5" r:id="rId7"/>
+    <sheet name="ID_MAXERR" sheetId="6" r:id="rId8"/>
+    <sheet name="FD_MAXERR" sheetId="7" r:id="rId9"/>
+    <sheet name="ID_PLOTS" sheetId="8" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
@@ -16,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="226">
   <si>
     <t>id_rmse</t>
   </si>
@@ -349,6 +353,351 @@
   </si>
   <si>
     <t>num_fd_samples</t>
+  </si>
+  <si>
+    <t>id_rmse</t>
+  </si>
+  <si>
+    <t>cad</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>phys</t>
+  </si>
+  <si>
+    <t>fd</t>
+  </si>
+  <si>
+    <t>j1</t>
+  </si>
+  <si>
+    <t>j2</t>
+  </si>
+  <si>
+    <t>j3</t>
+  </si>
+  <si>
+    <t>j4</t>
+  </si>
+  <si>
+    <t>j5</t>
+  </si>
+  <si>
+    <t>j6</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>fd_rmse</t>
+  </si>
+  <si>
+    <t>qd_cad</t>
+  </si>
+  <si>
+    <t>qd_min</t>
+  </si>
+  <si>
+    <t>qd_rec</t>
+  </si>
+  <si>
+    <t>qd_phys</t>
+  </si>
+  <si>
+    <t>qd_fd</t>
+  </si>
+  <si>
+    <t>cad</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>phys</t>
+  </si>
+  <si>
+    <t>fd</t>
+  </si>
+  <si>
+    <t>j1</t>
+  </si>
+  <si>
+    <t>j2</t>
+  </si>
+  <si>
+    <t>j3</t>
+  </si>
+  <si>
+    <t>j4</t>
+  </si>
+  <si>
+    <t>j5</t>
+  </si>
+  <si>
+    <t>j6</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>csv_file</t>
+  </si>
+  <si>
+    <t>/home/lsn/model/model_e1/applications/Body_GravityPara_Iden/test/../data/excitation/PD-M1-v0_multi_joint_20260305-195432_exctra_real.csv</t>
+  </si>
+  <si>
+    <t>num_samples</t>
+  </si>
+  <si>
+    <t>num_fd_samples</t>
+  </si>
+  <si>
+    <t>id_compare_png</t>
+  </si>
+  <si>
+    <t>/home/lsn/model/model_e1/applications/Body_GravityPara_Iden/test/../build/id_compare_plot.png</t>
+  </si>
+  <si>
+    <t>id_error_png</t>
+  </si>
+  <si>
+    <t>/home/lsn/model/model_e1/applications/Body_GravityPara_Iden/test/../build/id_error_plot.png</t>
+  </si>
+  <si>
+    <t>id_rmse</t>
+  </si>
+  <si>
+    <t>cad</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>phys</t>
+  </si>
+  <si>
+    <t>fd</t>
+  </si>
+  <si>
+    <t>j1</t>
+  </si>
+  <si>
+    <t>j2</t>
+  </si>
+  <si>
+    <t>j3</t>
+  </si>
+  <si>
+    <t>j4</t>
+  </si>
+  <si>
+    <t>j5</t>
+  </si>
+  <si>
+    <t>j6</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>fd_rmse</t>
+  </si>
+  <si>
+    <t>qd_cad</t>
+  </si>
+  <si>
+    <t>qd_min</t>
+  </si>
+  <si>
+    <t>qd_rec</t>
+  </si>
+  <si>
+    <t>qd_phys</t>
+  </si>
+  <si>
+    <t>qd_fd</t>
+  </si>
+  <si>
+    <t>cad</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>phys</t>
+  </si>
+  <si>
+    <t>fd</t>
+  </si>
+  <si>
+    <t>j1</t>
+  </si>
+  <si>
+    <t>j2</t>
+  </si>
+  <si>
+    <t>j3</t>
+  </si>
+  <si>
+    <t>j4</t>
+  </si>
+  <si>
+    <t>j5</t>
+  </si>
+  <si>
+    <t>j6</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>id_maxerr</t>
+  </si>
+  <si>
+    <t>cad</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>phys</t>
+  </si>
+  <si>
+    <t>fd</t>
+  </si>
+  <si>
+    <t>j1</t>
+  </si>
+  <si>
+    <t>j2</t>
+  </si>
+  <si>
+    <t>j3</t>
+  </si>
+  <si>
+    <t>j4</t>
+  </si>
+  <si>
+    <t>j5</t>
+  </si>
+  <si>
+    <t>j6</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>fd_maxerr</t>
+  </si>
+  <si>
+    <t>qd_cad</t>
+  </si>
+  <si>
+    <t>qd_min</t>
+  </si>
+  <si>
+    <t>qd_rec</t>
+  </si>
+  <si>
+    <t>qd_phys</t>
+  </si>
+  <si>
+    <t>qd_fd</t>
+  </si>
+  <si>
+    <t>cad</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>phys</t>
+  </si>
+  <si>
+    <t>fd</t>
+  </si>
+  <si>
+    <t>j1</t>
+  </si>
+  <si>
+    <t>j2</t>
+  </si>
+  <si>
+    <t>j3</t>
+  </si>
+  <si>
+    <t>j4</t>
+  </si>
+  <si>
+    <t>j5</t>
+  </si>
+  <si>
+    <t>j6</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>csv_file</t>
+  </si>
+  <si>
+    <t>/home/lsn/model/model_e1/applications/Body_GravityPara_Iden/test/../data/excitation/PD-M1-v0_multi_joint_20260305-195432_exctra_real.csv</t>
+  </si>
+  <si>
+    <t>num_samples</t>
+  </si>
+  <si>
+    <t>num_fd_samples</t>
+  </si>
+  <si>
+    <t>id_compare_png</t>
+  </si>
+  <si>
+    <t>/home/lsn/model/model_e1/applications/Body_GravityPara_Iden/test/../build/id_compare_plot.png</t>
+  </si>
+  <si>
+    <t>id_error_png</t>
+  </si>
+  <si>
+    <t>/home/lsn/model/model_e1/applications/Body_GravityPara_Iden/test/../build/id_error_plot.png</t>
   </si>
 </sst>
 </file>
@@ -369,7 +718,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -386,11 +735,21 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
@@ -401,6 +760,16 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -426,36 +795,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>74</v>
+        <v>152</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>83</v>
+        <v>161</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>84</v>
+        <v>162</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>85</v>
+        <v>163</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>87</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="B2" s="0">
         <v>25.133675083377792</v>
@@ -484,7 +853,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="B3" s="0">
         <v>21.76313210642531</v>
@@ -513,7 +882,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="B4" s="0">
         <v>21.783348040775511</v>
@@ -542,7 +911,7 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="B5" s="0">
         <v>23.393958287947715</v>
@@ -571,7 +940,7 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="B6" s="0">
         <v>23.349844310268359</v>
@@ -620,321 +989,321 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>88</v>
+        <v>166</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>99</v>
+        <v>177</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>100</v>
+        <v>178</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>102</v>
+        <v>180</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>103</v>
+        <v>181</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>104</v>
+        <v>182</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>105</v>
+        <v>183</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>106</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="B2" s="0">
-        <v>17.330921290213421</v>
+        <v>21.814588930814715</v>
       </c>
       <c r="C2" s="0">
-        <v>6.6417872304006904</v>
+        <v>11.309096518789065</v>
       </c>
       <c r="D2" s="0">
-        <v>6.9088928089369981</v>
+        <v>12.557416575416211</v>
       </c>
       <c r="E2" s="0">
-        <v>5.5033340882910613</v>
+        <v>16.10750901624241</v>
       </c>
       <c r="F2" s="0">
-        <v>6.4065239848684108</v>
+        <v>19.61132623175909</v>
       </c>
       <c r="G2" s="0">
-        <v>5.7715929935991577</v>
+        <v>10.283316577742646</v>
       </c>
       <c r="H2" s="0">
-        <v>8.0938420660516233</v>
+        <v>15.28054230846069</v>
       </c>
       <c r="I2" s="0">
-        <v>17.330921290213421</v>
+        <v>21.814588930814715</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>90</v>
+        <v>168</v>
       </c>
       <c r="B3" s="0">
-        <v>27328908.772966035</v>
+        <v>101153042.05615146</v>
       </c>
       <c r="C3" s="0">
-        <v>14767070.411030246</v>
+        <v>109408918.40382653</v>
       </c>
       <c r="D3" s="0">
-        <v>13204179.004801404</v>
+        <v>20990188.093777418</v>
       </c>
       <c r="E3" s="0">
-        <v>16433067.291073076</v>
+        <v>29733561.664996136</v>
       </c>
       <c r="F3" s="0">
-        <v>71074616.456191108</v>
+        <v>139729349.44422689</v>
       </c>
       <c r="G3" s="0">
-        <v>36329118.248555869</v>
+        <v>63826116.684476711</v>
       </c>
       <c r="H3" s="0">
-        <v>29856160.03076962</v>
+        <v>77473529.391242519</v>
       </c>
       <c r="I3" s="0">
-        <v>71074616.456191108</v>
+        <v>139729349.44422689</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>91</v>
+        <v>169</v>
       </c>
       <c r="B4" s="0">
-        <v>27444377.805836305</v>
+        <v>100622432.74253353</v>
       </c>
       <c r="C4" s="0">
-        <v>14659671.643100342</v>
+        <v>110816909.29127499</v>
       </c>
       <c r="D4" s="0">
-        <v>13254170.768211056</v>
+        <v>20661941.969125152</v>
       </c>
       <c r="E4" s="0">
-        <v>16727208.663149929</v>
+        <v>29999290.106963821</v>
       </c>
       <c r="F4" s="0">
-        <v>72361668.967769951</v>
+        <v>141221833.86502314</v>
       </c>
       <c r="G4" s="0">
-        <v>36419458.756647401</v>
+        <v>63779398.489535436</v>
       </c>
       <c r="H4" s="0">
-        <v>30144426.100785833</v>
+        <v>77850301.077409342</v>
       </c>
       <c r="I4" s="0">
-        <v>72361668.967769951</v>
+        <v>141221833.86502314</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>92</v>
+        <v>170</v>
       </c>
       <c r="B5" s="0">
-        <v>36.899047493615598</v>
+        <v>53.742699134669763</v>
       </c>
       <c r="C5" s="0">
-        <v>16.285317701312227</v>
+        <v>18.832390747117945</v>
       </c>
       <c r="D5" s="0">
-        <v>16.800892603830299</v>
+        <v>27.546735503606655</v>
       </c>
       <c r="E5" s="0">
-        <v>14.421867199121667</v>
+        <v>18.338247882348469</v>
       </c>
       <c r="F5" s="0">
-        <v>134.71604439881932</v>
+        <v>227.39927116076518</v>
       </c>
       <c r="G5" s="0">
-        <v>52.637184426270615</v>
+        <v>77.784500999813602</v>
       </c>
       <c r="H5" s="0">
-        <v>45.293392303828284</v>
+        <v>70.607307571386926</v>
       </c>
       <c r="I5" s="0">
-        <v>134.71604439881932</v>
+        <v>227.39927116076518</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="B6" s="0">
-        <v>5.893327064238548</v>
+        <v>14.635794950496395</v>
       </c>
       <c r="C6" s="0">
-        <v>3.205755268369749</v>
+        <v>26.602985954465399</v>
       </c>
       <c r="D6" s="0">
-        <v>2.047774379467783</v>
+        <v>10.090977426514192</v>
       </c>
       <c r="E6" s="0">
-        <v>11.980768156016866</v>
+        <v>15.422611038151196</v>
       </c>
       <c r="F6" s="0">
-        <v>85.175371572471064</v>
+        <v>312.3081049500957</v>
       </c>
       <c r="G6" s="0">
-        <v>6.8901975613367892</v>
+        <v>36.281446031435713</v>
       </c>
       <c r="H6" s="0">
-        <v>19.198865666983469</v>
+        <v>69.22365339185977</v>
       </c>
       <c r="I6" s="0">
-        <v>85.175371572471064</v>
+        <v>312.3081049500957</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>94</v>
+        <v>172</v>
       </c>
       <c r="B7" s="0">
-        <v>98.413153420524665</v>
+        <v>131.75862406332038</v>
       </c>
       <c r="C7" s="0">
-        <v>46.148142300996064</v>
+        <v>84.170711577692018</v>
       </c>
       <c r="D7" s="0">
-        <v>39.268912753178903</v>
+        <v>69.040434125410883</v>
       </c>
       <c r="E7" s="0">
-        <v>40.14462921788536</v>
+        <v>126.69777719370305</v>
       </c>
       <c r="F7" s="0">
-        <v>55.857672981227367</v>
+        <v>112.58044152134183</v>
       </c>
       <c r="G7" s="0">
-        <v>69.864332508618304</v>
+        <v>111.91667824728752</v>
       </c>
       <c r="H7" s="0">
-        <v>58.282807197071776</v>
+        <v>106.02744445479262</v>
       </c>
       <c r="I7" s="0">
-        <v>98.413153420524665</v>
+        <v>131.75862406332038</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>95</v>
+        <v>173</v>
       </c>
       <c r="B8" s="0">
-        <v>117492551.97978444</v>
+        <v>411297134.09456301</v>
       </c>
       <c r="C8" s="0">
-        <v>72376430.277319804</v>
+        <v>346167298.25467241</v>
       </c>
       <c r="D8" s="0">
-        <v>58217270.797635354</v>
+        <v>125528409.9973544</v>
       </c>
       <c r="E8" s="0">
-        <v>74568365.808137074</v>
+        <v>106206359.08697316</v>
       </c>
       <c r="F8" s="0">
-        <v>322219334.56321394</v>
+        <v>543579550.44534481</v>
       </c>
       <c r="G8" s="0">
-        <v>169413071.87688309</v>
+        <v>251767376.13551322</v>
       </c>
       <c r="H8" s="0">
-        <v>135714504.21716228</v>
+        <v>297424354.66907018</v>
       </c>
       <c r="I8" s="0">
-        <v>322219334.56321394</v>
+        <v>543579550.44534481</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="B9" s="0">
-        <v>117706796.78119019</v>
+        <v>406211555.80851865</v>
       </c>
       <c r="C9" s="0">
-        <v>71965213.658180848</v>
+        <v>341941652.9007495</v>
       </c>
       <c r="D9" s="0">
-        <v>58347659.690781988</v>
+        <v>122881023.20334454</v>
       </c>
       <c r="E9" s="0">
-        <v>75644360.263448194</v>
+        <v>107077963.21854144</v>
       </c>
       <c r="F9" s="0">
-        <v>327440435.8198235</v>
+        <v>544569044.4712621</v>
       </c>
       <c r="G9" s="0">
-        <v>169476117.03296834</v>
+        <v>249224059.57976842</v>
       </c>
       <c r="H9" s="0">
-        <v>136763430.54106548</v>
+        <v>295317549.86369741</v>
       </c>
       <c r="I9" s="0">
-        <v>327440435.8198235</v>
+        <v>544569044.4712621</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="B10" s="0">
-        <v>200.9907955086567</v>
+        <v>179.54404698018593</v>
       </c>
       <c r="C10" s="0">
-        <v>111.92991669406831</v>
+        <v>120.06036533465969</v>
       </c>
       <c r="D10" s="0">
-        <v>88.186450265094024</v>
+        <v>89.449677723220972</v>
       </c>
       <c r="E10" s="0">
-        <v>62.345196266769101</v>
+        <v>92.648185675578773</v>
       </c>
       <c r="F10" s="0">
-        <v>575.82373653179923</v>
+        <v>818.47690565903088</v>
       </c>
       <c r="G10" s="0">
-        <v>219.0632216162042</v>
+        <v>344.17125388756625</v>
       </c>
       <c r="H10" s="0">
-        <v>209.72321948043191</v>
+        <v>274.05840587670713</v>
       </c>
       <c r="I10" s="0">
-        <v>575.82373653179923</v>
+        <v>818.47690565903088</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="B11" s="0">
-        <v>66.101355342056308</v>
+        <v>106.62993332271776</v>
       </c>
       <c r="C11" s="0">
-        <v>41.695882512290808</v>
+        <v>78.304582090474824</v>
       </c>
       <c r="D11" s="0">
-        <v>30.262015826549664</v>
+        <v>46.242247195855143</v>
       </c>
       <c r="E11" s="0">
-        <v>50.344564545196675</v>
+        <v>41.121707551479368</v>
       </c>
       <c r="F11" s="0">
-        <v>356.63419090270077</v>
+        <v>303.81081135737338</v>
       </c>
       <c r="G11" s="0">
-        <v>82.015430216359235</v>
+        <v>168.42261026750973</v>
       </c>
       <c r="H11" s="0">
-        <v>104.50890655752558</v>
+        <v>124.08864863090169</v>
       </c>
       <c r="I11" s="0">
-        <v>356.63419090270077</v>
+        <v>303.81081135737338</v>
       </c>
     </row>
   </sheetData>
@@ -953,24 +1322,615 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>107</v>
+        <v>218</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>110</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="B2" s="0">
         <v>1001</v>
       </c>
       <c r="C2" s="0">
+        <v>1001</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" customWidth="true"/>
+    <col min="2" max="2" width="12.5703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.140625" customWidth="true"/>
+    <col min="2" max="2" width="11.7109375" customWidth="true"/>
+    <col min="3" max="3" width="11.7109375" customWidth="true"/>
+    <col min="4" max="4" width="11.7109375" customWidth="true"/>
+    <col min="5" max="5" width="11.7109375" customWidth="true"/>
+    <col min="6" max="6" width="11.7109375" customWidth="true"/>
+    <col min="7" max="7" width="11.7109375" customWidth="true"/>
+    <col min="8" max="8" width="11.7109375" customWidth="true"/>
+    <col min="9" max="9" width="11.7109375" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" s="0">
+        <v>62.517384276211828</v>
+      </c>
+      <c r="C2" s="0">
+        <v>119.33294079652336</v>
+      </c>
+      <c r="D2" s="0">
+        <v>87.939965716602671</v>
+      </c>
+      <c r="E2" s="0">
+        <v>32.424099282112486</v>
+      </c>
+      <c r="F2" s="0">
+        <v>5.2920023596754717</v>
+      </c>
+      <c r="G2" s="0">
+        <v>2.5825018997508979</v>
+      </c>
+      <c r="H2" s="0">
+        <v>51.681482388479452</v>
+      </c>
+      <c r="I2" s="0">
+        <v>119.33294079652336</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="0">
+        <v>61.966663239826893</v>
+      </c>
+      <c r="C3" s="0">
+        <v>46.520117832881276</v>
+      </c>
+      <c r="D3" s="0">
+        <v>82.425480628711711</v>
+      </c>
+      <c r="E3" s="0">
+        <v>24.128643126476433</v>
+      </c>
+      <c r="F3" s="0">
+        <v>16.172090080281318</v>
+      </c>
+      <c r="G3" s="0">
+        <v>8.8289505676761024</v>
+      </c>
+      <c r="H3" s="0">
+        <v>40.006990912642294</v>
+      </c>
+      <c r="I3" s="0">
+        <v>82.425480628711711</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" s="0">
+        <v>61.949865290842666</v>
+      </c>
+      <c r="C4" s="0">
+        <v>47.164052873294331</v>
+      </c>
+      <c r="D4" s="0">
+        <v>82.512621780138005</v>
+      </c>
+      <c r="E4" s="0">
+        <v>24.064410602922557</v>
+      </c>
+      <c r="F4" s="0">
+        <v>16.095366260934071</v>
+      </c>
+      <c r="G4" s="0">
+        <v>8.7656244838394883</v>
+      </c>
+      <c r="H4" s="0">
+        <v>40.091990215328515</v>
+      </c>
+      <c r="I4" s="0">
+        <v>82.512621780138005</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="B5" s="0">
+        <v>59.465685456404593</v>
+      </c>
+      <c r="C5" s="0">
+        <v>94.44588805851069</v>
+      </c>
+      <c r="D5" s="0">
+        <v>83.64818100714902</v>
+      </c>
+      <c r="E5" s="0">
+        <v>27.319097665836093</v>
+      </c>
+      <c r="F5" s="0">
+        <v>5.740006919920658</v>
+      </c>
+      <c r="G5" s="0">
+        <v>3.0596412234858716</v>
+      </c>
+      <c r="H5" s="0">
+        <v>45.613083388551154</v>
+      </c>
+      <c r="I5" s="0">
+        <v>94.44588805851069</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="0">
+        <v>58.002006900747503</v>
+      </c>
+      <c r="C6" s="0">
+        <v>61.153687036925099</v>
+      </c>
+      <c r="D6" s="0">
+        <v>84.242024724906344</v>
+      </c>
+      <c r="E6" s="0">
+        <v>24.686194548994546</v>
+      </c>
+      <c r="F6" s="0">
+        <v>7.6622213507474406</v>
+      </c>
+      <c r="G6" s="0">
+        <v>4.6381918310868588</v>
+      </c>
+      <c r="H6" s="0">
+        <v>40.064054398901298</v>
+      </c>
+      <c r="I6" s="0">
+        <v>84.242024724906344</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.28515625" customWidth="true"/>
+    <col min="2" max="2" width="11.7109375" customWidth="true"/>
+    <col min="3" max="3" width="11.7109375" customWidth="true"/>
+    <col min="4" max="4" width="11.7109375" customWidth="true"/>
+    <col min="5" max="5" width="11.7109375" customWidth="true"/>
+    <col min="6" max="6" width="11.7109375" customWidth="true"/>
+    <col min="7" max="7" width="11.7109375" customWidth="true"/>
+    <col min="8" max="8" width="11.7109375" customWidth="true"/>
+    <col min="9" max="9" width="11.7109375" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
         <v>200</v>
+      </c>
+      <c r="B2" s="0">
+        <v>40.143872116836619</v>
+      </c>
+      <c r="C2" s="0">
+        <v>29.31150608313331</v>
+      </c>
+      <c r="D2" s="0">
+        <v>23.969811384964917</v>
+      </c>
+      <c r="E2" s="0">
+        <v>34.404947810027373</v>
+      </c>
+      <c r="F2" s="0">
+        <v>35.095138006163793</v>
+      </c>
+      <c r="G2" s="0">
+        <v>21.925539229845661</v>
+      </c>
+      <c r="H2" s="0">
+        <v>30.808469105161944</v>
+      </c>
+      <c r="I2" s="0">
+        <v>40.143872116836619</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="B3" s="0">
+        <v>180759408.3360402</v>
+      </c>
+      <c r="C3" s="0">
+        <v>219677539.30321875</v>
+      </c>
+      <c r="D3" s="0">
+        <v>41471583.978499584</v>
+      </c>
+      <c r="E3" s="0">
+        <v>58207875.21772594</v>
+      </c>
+      <c r="F3" s="0">
+        <v>278694671.11311811</v>
+      </c>
+      <c r="G3" s="0">
+        <v>126707467.66742155</v>
+      </c>
+      <c r="H3" s="0">
+        <v>150919757.6026707</v>
+      </c>
+      <c r="I3" s="0">
+        <v>278694671.11311811</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="B4" s="0">
+        <v>179012321.62594005</v>
+      </c>
+      <c r="C4" s="0">
+        <v>218927468.9535172</v>
+      </c>
+      <c r="D4" s="0">
+        <v>40700505.324201524</v>
+      </c>
+      <c r="E4" s="0">
+        <v>58407251.350707158</v>
+      </c>
+      <c r="F4" s="0">
+        <v>279980799.23794037</v>
+      </c>
+      <c r="G4" s="0">
+        <v>125978133.0353758</v>
+      </c>
+      <c r="H4" s="0">
+        <v>150501079.92128035</v>
+      </c>
+      <c r="I4" s="0">
+        <v>279980799.23794037</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" s="0">
+        <v>70.095484251227347</v>
+      </c>
+      <c r="C5" s="0">
+        <v>35.681137759063176</v>
+      </c>
+      <c r="D5" s="0">
+        <v>37.78260374806834</v>
+      </c>
+      <c r="E5" s="0">
+        <v>30.688075473881611</v>
+      </c>
+      <c r="F5" s="0">
+        <v>429.45331944420064</v>
+      </c>
+      <c r="G5" s="0">
+        <v>124.73610340993991</v>
+      </c>
+      <c r="H5" s="0">
+        <v>121.4061206810635</v>
+      </c>
+      <c r="I5" s="0">
+        <v>429.45331944420064</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" s="0">
+        <v>40.659027715372197</v>
+      </c>
+      <c r="C6" s="0">
+        <v>50.385034329906283</v>
+      </c>
+      <c r="D6" s="0">
+        <v>19.862830668616198</v>
+      </c>
+      <c r="E6" s="0">
+        <v>22.104357171716824</v>
+      </c>
+      <c r="F6" s="0">
+        <v>443.88146717628126</v>
+      </c>
+      <c r="G6" s="0">
+        <v>68.65949558540018</v>
+      </c>
+      <c r="H6" s="0">
+        <v>107.59203544121549</v>
+      </c>
+      <c r="I6" s="0">
+        <v>443.88146717628126</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="0">
+        <v>396.62616691702516</v>
+      </c>
+      <c r="C7" s="0">
+        <v>216.14271771950135</v>
+      </c>
+      <c r="D7" s="0">
+        <v>364.32205079469168</v>
+      </c>
+      <c r="E7" s="0">
+        <v>500.05312286441449</v>
+      </c>
+      <c r="F7" s="0">
+        <v>354.64082503683505</v>
+      </c>
+      <c r="G7" s="0">
+        <v>299.36191606688283</v>
+      </c>
+      <c r="H7" s="0">
+        <v>355.19113323322512</v>
+      </c>
+      <c r="I7" s="0">
+        <v>500.05312286441449</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" s="0">
+        <v>1283050979.2834609</v>
+      </c>
+      <c r="C8" s="0">
+        <v>1092783412.8530481</v>
+      </c>
+      <c r="D8" s="0">
+        <v>316977613.75162113</v>
+      </c>
+      <c r="E8" s="0">
+        <v>319850889.25241286</v>
+      </c>
+      <c r="F8" s="0">
+        <v>1343759383.5737145</v>
+      </c>
+      <c r="G8" s="0">
+        <v>708450933.87249506</v>
+      </c>
+      <c r="H8" s="0">
+        <v>844145535.43112528</v>
+      </c>
+      <c r="I8" s="0">
+        <v>1343759383.5737145</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="B9" s="0">
+        <v>1258909787.2888856</v>
+      </c>
+      <c r="C9" s="0">
+        <v>1098473887.4599104</v>
+      </c>
+      <c r="D9" s="0">
+        <v>307040345.39289343</v>
+      </c>
+      <c r="E9" s="0">
+        <v>322881967.24906963</v>
+      </c>
+      <c r="F9" s="0">
+        <v>1343478610.4420049</v>
+      </c>
+      <c r="G9" s="0">
+        <v>694196965.68109894</v>
+      </c>
+      <c r="H9" s="0">
+        <v>837496927.2523104</v>
+      </c>
+      <c r="I9" s="0">
+        <v>1343478610.4420049</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="B10" s="0">
+        <v>544.96591774532624</v>
+      </c>
+      <c r="C10" s="0">
+        <v>344.38013643360802</v>
+      </c>
+      <c r="D10" s="0">
+        <v>308.714566966961</v>
+      </c>
+      <c r="E10" s="0">
+        <v>311.53902481978309</v>
+      </c>
+      <c r="F10" s="0">
+        <v>2479.960680247972</v>
+      </c>
+      <c r="G10" s="0">
+        <v>1002.9417137975147</v>
+      </c>
+      <c r="H10" s="0">
+        <v>832.08367333519425</v>
+      </c>
+      <c r="I10" s="0">
+        <v>2479.960680247972</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="B11" s="0">
+        <v>279.14453884555945</v>
+      </c>
+      <c r="C11" s="0">
+        <v>236.33774085122508</v>
+      </c>
+      <c r="D11" s="0">
+        <v>178.12791631819789</v>
+      </c>
+      <c r="E11" s="0">
+        <v>118.87861885190506</v>
+      </c>
+      <c r="F11" s="0">
+        <v>729.44204537000985</v>
+      </c>
+      <c r="G11" s="0">
+        <v>554.15826594109274</v>
+      </c>
+      <c r="H11" s="0">
+        <v>349.34818769633171</v>
+      </c>
+      <c r="I11" s="0">
+        <v>729.44204537000985</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" customWidth="true"/>
+    <col min="2" max="2" width="12.5703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>
